--- a/artfynd/A 46794-2021 artfynd.xlsx
+++ b/artfynd/A 46794-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46794-2021 artfynd.xlsx
+++ b/artfynd/A 46794-2021 artfynd.xlsx
@@ -11082,7 +11082,7 @@
         <v>101789275</v>
       </c>
       <c r="B91" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11126,10 +11126,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>382226.2781316615</v>
+        <v>382226</v>
       </c>
       <c r="R91" t="n">
-        <v>6705964.082612941</v>
+        <v>6705964</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -11159,19 +11159,9 @@
           <t>2022-06-21</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2022-06-21</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11198,10 +11188,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117675710</v>
+        <v>117675720</v>
       </c>
       <c r="B92" t="n">
-        <v>78569</v>
+        <v>78502</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11210,25 +11200,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6450</v>
+        <v>184</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Broktagel</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bryoria bicolor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ehrh.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11238,10 +11228,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>382245</v>
+        <v>381772</v>
       </c>
       <c r="R92" t="n">
-        <v>6706170</v>
+        <v>6705774</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11300,10 +11290,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117675720</v>
+        <v>117675712</v>
       </c>
       <c r="B93" t="n">
-        <v>78502</v>
+        <v>78480</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11312,25 +11302,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>184</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Broktagel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria bicolor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ehrh.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11340,10 +11330,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>381772</v>
+        <v>382154</v>
       </c>
       <c r="R93" t="n">
-        <v>6705774</v>
+        <v>6706123</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11402,10 +11392,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117675711</v>
+        <v>117675714</v>
       </c>
       <c r="B94" t="n">
-        <v>78480</v>
+        <v>86816</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11418,21 +11408,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11442,10 +11432,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>382234</v>
+        <v>382050</v>
       </c>
       <c r="R94" t="n">
-        <v>6706152</v>
+        <v>6705912</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11504,10 +11494,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117675716</v>
+        <v>117675717</v>
       </c>
       <c r="B95" t="n">
-        <v>78514</v>
+        <v>78569</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11516,25 +11506,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>185</v>
+        <v>6450</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11544,10 +11534,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>382013</v>
+        <v>381938</v>
       </c>
       <c r="R95" t="n">
-        <v>6705934</v>
+        <v>6705932</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11606,10 +11596,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117675713</v>
+        <v>117675711</v>
       </c>
       <c r="B96" t="n">
-        <v>78569</v>
+        <v>78480</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11618,25 +11608,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11646,10 +11636,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>382052</v>
+        <v>382234</v>
       </c>
       <c r="R96" t="n">
-        <v>6705916</v>
+        <v>6706152</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11708,10 +11698,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>117675717</v>
+        <v>117675716</v>
       </c>
       <c r="B97" t="n">
-        <v>78569</v>
+        <v>78514</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11720,25 +11710,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6450</v>
+        <v>185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11748,10 +11738,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>381938</v>
+        <v>382013</v>
       </c>
       <c r="R97" t="n">
-        <v>6705932</v>
+        <v>6705934</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11810,10 +11800,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>117675719</v>
+        <v>117675708</v>
       </c>
       <c r="B98" t="n">
-        <v>78569</v>
+        <v>82259</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11822,25 +11812,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11850,10 +11840,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>381820</v>
+        <v>382253</v>
       </c>
       <c r="R98" t="n">
-        <v>6705940</v>
+        <v>6706147</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11894,6 +11884,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11912,10 +11903,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>117675714</v>
+        <v>117675709</v>
       </c>
       <c r="B99" t="n">
-        <v>86816</v>
+        <v>78643</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11924,25 +11915,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>510</v>
+        <v>1249</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11952,10 +11943,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>382050</v>
+        <v>382250</v>
       </c>
       <c r="R99" t="n">
-        <v>6705912</v>
+        <v>6706168</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12014,10 +12005,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117675707</v>
+        <v>117675719</v>
       </c>
       <c r="B100" t="n">
-        <v>82259</v>
+        <v>78569</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12026,25 +12017,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12054,10 +12045,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>382255</v>
+        <v>381820</v>
       </c>
       <c r="R100" t="n">
-        <v>6706153</v>
+        <v>6705940</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12098,7 +12089,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -12117,10 +12107,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>117675712</v>
+        <v>117675715</v>
       </c>
       <c r="B101" t="n">
-        <v>78480</v>
+        <v>78569</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12129,25 +12119,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12157,10 +12147,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>382154</v>
+        <v>382028</v>
       </c>
       <c r="R101" t="n">
-        <v>6706123</v>
+        <v>6705961</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12219,10 +12209,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117675708</v>
+        <v>117675710</v>
       </c>
       <c r="B102" t="n">
-        <v>82259</v>
+        <v>78569</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12231,25 +12221,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12259,10 +12249,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>382253</v>
+        <v>382245</v>
       </c>
       <c r="R102" t="n">
-        <v>6706147</v>
+        <v>6706170</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12303,7 +12293,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -12322,10 +12311,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117675709</v>
+        <v>117675713</v>
       </c>
       <c r="B103" t="n">
-        <v>78643</v>
+        <v>78569</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12334,25 +12323,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1249</v>
+        <v>6450</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12362,10 +12351,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>382250</v>
+        <v>382052</v>
       </c>
       <c r="R103" t="n">
-        <v>6706168</v>
+        <v>6705916</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12424,10 +12413,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>117675715</v>
+        <v>117675707</v>
       </c>
       <c r="B104" t="n">
-        <v>78569</v>
+        <v>82259</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12436,25 +12425,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12464,10 +12453,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>382028</v>
+        <v>382255</v>
       </c>
       <c r="R104" t="n">
-        <v>6705961</v>
+        <v>6706153</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12508,6 +12497,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46794-2021 artfynd.xlsx
+++ b/artfynd/A 46794-2021 artfynd.xlsx
@@ -11188,10 +11188,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117675720</v>
+        <v>117675711</v>
       </c>
       <c r="B92" t="n">
-        <v>78502</v>
+        <v>78482</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11200,25 +11200,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>184</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Broktagel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria bicolor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ehrh.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11228,10 +11228,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>381772</v>
+        <v>382234</v>
       </c>
       <c r="R92" t="n">
-        <v>6705774</v>
+        <v>6706152</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11290,10 +11290,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117675712</v>
+        <v>117675714</v>
       </c>
       <c r="B93" t="n">
-        <v>78480</v>
+        <v>86818</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11306,21 +11306,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11330,10 +11330,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>382154</v>
+        <v>382050</v>
       </c>
       <c r="R93" t="n">
-        <v>6706123</v>
+        <v>6705912</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11392,10 +11392,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117675714</v>
+        <v>117675715</v>
       </c>
       <c r="B94" t="n">
-        <v>86816</v>
+        <v>78571</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11404,25 +11404,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>510</v>
+        <v>6450</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11432,10 +11432,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>382050</v>
+        <v>382028</v>
       </c>
       <c r="R94" t="n">
-        <v>6705912</v>
+        <v>6705961</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11494,10 +11494,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117675717</v>
+        <v>117675712</v>
       </c>
       <c r="B95" t="n">
-        <v>78569</v>
+        <v>78482</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11506,25 +11506,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11534,10 +11534,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>381938</v>
+        <v>382154</v>
       </c>
       <c r="R95" t="n">
-        <v>6705932</v>
+        <v>6706123</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11596,10 +11596,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117675711</v>
+        <v>117675707</v>
       </c>
       <c r="B96" t="n">
-        <v>78480</v>
+        <v>82261</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11612,21 +11612,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11636,10 +11636,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>382234</v>
+        <v>382255</v>
       </c>
       <c r="R96" t="n">
-        <v>6706152</v>
+        <v>6706153</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11680,6 +11680,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11701,7 +11702,7 @@
         <v>117675716</v>
       </c>
       <c r="B97" t="n">
-        <v>78514</v>
+        <v>78516</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11803,7 +11804,7 @@
         <v>117675708</v>
       </c>
       <c r="B98" t="n">
-        <v>82259</v>
+        <v>82261</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11903,10 +11904,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>117675709</v>
+        <v>117675710</v>
       </c>
       <c r="B99" t="n">
-        <v>78643</v>
+        <v>78571</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11915,25 +11916,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1249</v>
+        <v>6450</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11943,10 +11944,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>382250</v>
+        <v>382245</v>
       </c>
       <c r="R99" t="n">
-        <v>6706168</v>
+        <v>6706170</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12005,10 +12006,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>117675719</v>
+        <v>117675709</v>
       </c>
       <c r="B100" t="n">
-        <v>78569</v>
+        <v>78645</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12017,25 +12018,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6450</v>
+        <v>1249</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12045,10 +12046,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>381820</v>
+        <v>382250</v>
       </c>
       <c r="R100" t="n">
-        <v>6705940</v>
+        <v>6706168</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12107,10 +12108,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>117675715</v>
+        <v>117675713</v>
       </c>
       <c r="B101" t="n">
-        <v>78569</v>
+        <v>78571</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12147,10 +12148,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>382028</v>
+        <v>382052</v>
       </c>
       <c r="R101" t="n">
-        <v>6705961</v>
+        <v>6705916</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12209,10 +12210,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117675710</v>
+        <v>117675719</v>
       </c>
       <c r="B102" t="n">
-        <v>78569</v>
+        <v>78571</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12249,10 +12250,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>382245</v>
+        <v>381820</v>
       </c>
       <c r="R102" t="n">
-        <v>6706170</v>
+        <v>6705940</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12311,10 +12312,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117675713</v>
+        <v>117675720</v>
       </c>
       <c r="B103" t="n">
-        <v>78569</v>
+        <v>78504</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12323,25 +12324,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6450</v>
+        <v>184</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Broktagel</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bryoria bicolor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ehrh.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12351,10 +12352,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>382052</v>
+        <v>381772</v>
       </c>
       <c r="R103" t="n">
-        <v>6705916</v>
+        <v>6705774</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12413,10 +12414,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>117675707</v>
+        <v>117675717</v>
       </c>
       <c r="B104" t="n">
-        <v>82259</v>
+        <v>78571</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12425,25 +12426,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12453,10 +12454,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>382255</v>
+        <v>381938</v>
       </c>
       <c r="R104" t="n">
-        <v>6706153</v>
+        <v>6705932</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12497,7 +12498,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46794-2021 artfynd.xlsx
+++ b/artfynd/A 46794-2021 artfynd.xlsx
@@ -12210,10 +12210,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117675719</v>
+        <v>117675720</v>
       </c>
       <c r="B102" t="n">
-        <v>78571</v>
+        <v>78504</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12222,25 +12222,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6450</v>
+        <v>184</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Broktagel</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bryoria bicolor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ehrh.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12250,10 +12250,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>381820</v>
+        <v>381772</v>
       </c>
       <c r="R102" t="n">
-        <v>6705940</v>
+        <v>6705774</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12312,10 +12312,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>117675720</v>
+        <v>117675719</v>
       </c>
       <c r="B103" t="n">
-        <v>78504</v>
+        <v>78571</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12324,25 +12324,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>184</v>
+        <v>6450</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Broktagel</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria bicolor</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ehrh.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>381772</v>
+        <v>381820</v>
       </c>
       <c r="R103" t="n">
-        <v>6705774</v>
+        <v>6705940</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
